--- a/data/daily/2026-09/2026-09-04.xlsx
+++ b/data/daily/2026-09/2026-09-04.xlsx
@@ -1170,7 +1170,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="323850" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1220,14 +1220,64 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,7 +1425,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1475,27 +1475,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,24 +1553,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1578,79 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2906,7 +2906,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2914,34 +2914,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
@@ -3124,27 +3124,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>뉴트리디데이</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/4487367</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
         </is>
       </c>
     </row>
@@ -3693,17 +3693,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3750,19 +3750,19 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>뉴트리디데이</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3807,19 +3807,19 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3864,24 +3864,24 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
-        </is>
-      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>45,000원</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>30,900원</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>45,000원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,27 +4132,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
@@ -4167,34 +4167,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,27 +4202,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
@@ -4237,34 +4237,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314174&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306209&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260625/KRdkveXe1tokHnITW5go286314174_00_00KRdkveXe1tokHnITW5go.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/rS9JgHwoY8ffaFGoRZTx032306209_00_01rS9JgHwoY8ffaFGoRZTx.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,34 +4342,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4579,27 +4579,27 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>판티오</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
     </row>
@@ -4683,47 +4683,47 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1,500원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>grn+ 분홍이(105정)+초록이(70정) 기획세트 (35일분)</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>grn+</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186058&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018605852ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492943ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13,320원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,510원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627201ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670137ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[9/4 하루특가] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>49,800원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492943ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9/4 하루특가] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49,800원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,320원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846231ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[덴프스X카카오프렌즈] 덴마크 유산균이야기 30캡슐 1+1 기획 / 유산균이야기 우먼 기획 택 1</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30,080원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686145ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,47 +5330,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5382,52 +5382,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>grn+</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>바이탈뷰티</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>grn+ 분홍이(105정)+초록이(70정) 기획세트 (35일분)</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[9/4 하루특가] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[9/4 하루특가] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스X카카오프렌즈] 덴마크 유산균이야기 30캡슐 1+1 기획 / 유산균이야기 우먼 기획 택 1</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>13,320원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>27,510원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>49,800원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>9,600원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>49,800원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26,320원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>30,080원</t>
+          <t>11,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,29 +5667,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5699,19 +5699,19 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5721,13 +5721,13 @@
         <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5737,16 +5737,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -5755,29 +5755,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5809,19 +5809,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,12 +5831,78 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
